--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_system_switch.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_system_switch.xlsx
@@ -2859,7 +2859,7 @@
         <v>40</v>
       </c>
       <c r="E21" s="1">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
@@ -3452,10 +3452,10 @@
         <v>40</v>
       </c>
       <c r="E40" s="4">
-        <v>15</v>
+        <v>999</v>
       </c>
       <c r="F40" s="4">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>41</v>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_system_switch.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_system_switch.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_system_switch" sheetId="1" r:id="rId1"/>
@@ -2897,7 +2897,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="4">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="F22" s="4">
         <v>1</v>
@@ -3761,10 +3761,10 @@
         <v>1</v>
       </c>
       <c r="E52" s="4">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="F52" s="4">
-        <v>9999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -3781,10 +3781,10 @@
         <v>2</v>
       </c>
       <c r="E53" s="4">
-        <v>9999</v>
+        <v>600</v>
       </c>
       <c r="F53" s="4">
-        <v>9999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -3978,10 +3978,10 @@
         <v>1</v>
       </c>
       <c r="E63" s="4">
-        <v>9999</v>
+        <v>400</v>
       </c>
       <c r="F63" s="4">
-        <v>9999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:6">
